--- a/tests/golden/baseline/judge_export_excel_task.xlsx
+++ b/tests/golden/baseline/judge_export_excel_task.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[{'idx': 3, 'success': False, 'error': '模型调用超时'}]</t>
+          <t>[{'idx': 3, 'success': False, 'error': '模型调用超时', 'model_output': '', 'row_status': 'failed', 'user_input': '请写一个堆排序'}]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
